--- a/crm/v2/lgo/integral-top500-pharmavitale.xlsx
+++ b/crm/v2/lgo/integral-top500-pharmavitale.xlsx
@@ -642,7 +642,7 @@
         <v>221.32</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>212.71</v>
+        <v>212.74</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>163.7</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>157.33</v>
+        <v>157.36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>107.56</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>103.38</v>
+        <v>103.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>73.34</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>70.48999999999999</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>175.18</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>168.37</v>
+        <v>168.39</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>366.23</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>351.98</v>
+        <v>352.02</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>171.07</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>164.42</v>
+        <v>164.44</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>7.62</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>7.32</v>
+        <v>7.33</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>313.27</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>301.08</v>
+        <v>301.11</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>45.12</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>43.36</v>
+        <v>43.39</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>19.92</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>36.18</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>34.77</v>
+        <v>34.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>74.28</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>70.98999999999999</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136.5</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>4.41</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>181.48</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>174.42</v>
+        <v>174.45</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136.5</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>11.84</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>11.38</v>
+        <v>11.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>74.28</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>313.27</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>301.08</v>
+        <v>301.11</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>6.98</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>6.71</v>
+        <v>6.98</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>74.28</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>157.37</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>151.25</v>
+        <v>151.27</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>30.09</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>28.92</v>
+        <v>28.94</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>32.31</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>31.05</v>
+        <v>31.08</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>4.72</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>51.83</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>49.81</v>
+        <v>49.84</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>52.31</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>50.28</v>
+        <v>50.3</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>19.92</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>33.59</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>32.28</v>
+        <v>32.31</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>9.35</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>4.42</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>136.5</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>29.5</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>28.35</v>
+        <v>28.38</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>31.19</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>29.98</v>
+        <v>30</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>14.5</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>13.94</v>
+        <v>13.96</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>70.98999999999999</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>70.98999999999999</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>9.93</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>11.94</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>11.48</v>
+        <v>11.5</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>70.98999999999999</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>54.1</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>52</v>
+        <v>52.02</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>25.97</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>24.96</v>
+        <v>24.99</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>74.28</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>19.65</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>18.89</v>
+        <v>18.91</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>16.95</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>16.29</v>
+        <v>16.31</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>28.78</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>27.66</v>
+        <v>27.69</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>20.39</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>19.6</v>
+        <v>19.62</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>11.78</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>11.32</v>
+        <v>11.35</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>5.28</v>
       </c>
       <c r="D277" s="3" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>5.51</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>404.83</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>389.08</v>
+        <v>389.11</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>302.95</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>291.17</v>
+        <v>291.2</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -7677,10 +7677,10 @@
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>29.25</v>
+        <v>28.84</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>29.25</v>
+        <v>28.84</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>7.06</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>6.79</v>
+        <v>6.78</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="C324" s="3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>36.18</v>
       </c>
       <c r="D338" s="3" t="n">
-        <v>34.77</v>
+        <v>34.8</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>141.25</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>135.76</v>
+        <v>135.78</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>4.42</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>4.47</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>136.5</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>404.83</v>
       </c>
       <c r="D365" s="3" t="n">
-        <v>389.08</v>
+        <v>389.11</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>292.11</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>280.75</v>
+        <v>280.78</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>7.72</v>
+        <v>7.73</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>7.72</v>
+        <v>7.73</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>46.66</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>44.84</v>
+        <v>44.85</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>23.96</v>
+        <v>23.5</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>23.96</v>
+        <v>23.5</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>52.31</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>50.28</v>
+        <v>50.3</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>4.35</v>
       </c>
       <c r="D434" s="3" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>4.35</v>
       </c>
       <c r="D451" s="3" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
@@ -10874,10 +10874,10 @@
         </is>
       </c>
       <c r="C454" s="3" t="n">
-        <v>3.22</v>
+        <v>2.84</v>
       </c>
       <c r="D454" s="3" t="n">
-        <v>3.04</v>
+        <v>2.66</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>47.86</v>
       </c>
       <c r="D456" s="3" t="n">
-        <v>46</v>
+        <v>46.02</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45.12</v>
       </c>
       <c r="D459" s="3" t="n">
-        <v>43.36</v>
+        <v>43.39</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -11058,10 +11058,10 @@
         </is>
       </c>
       <c r="C462" s="3" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="D462" s="3" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>9.9</v>
       </c>
       <c r="D464" s="3" t="n">
-        <v>9.51</v>
+        <v>9.52</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>17.63</v>
       </c>
       <c r="D469" s="3" t="n">
-        <v>16.94</v>
+        <v>16.95</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         </is>
       </c>
       <c r="C473" s="3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="D473" s="3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>41.27</v>
       </c>
       <c r="D476" s="3" t="n">
-        <v>39.66</v>
+        <v>39.67</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -11426,10 +11426,10 @@
         </is>
       </c>
       <c r="C478" s="3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="D478" s="3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>349.93</v>
       </c>
       <c r="D486" s="3" t="n">
-        <v>336.32</v>
+        <v>336.35</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>7.05</v>
       </c>
       <c r="D487" s="3" t="n">
-        <v>6.78</v>
+        <v>6.77</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>23.68</v>
       </c>
       <c r="D490" s="3" t="n">
-        <v>22.76</v>
+        <v>22.79</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="C493" s="3" t="n">
-        <v>11.89</v>
+        <v>12.7</v>
       </c>
       <c r="D493" s="3" t="n">
-        <v>11.89</v>
+        <v>12.7</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>22.71</v>
       </c>
       <c r="D501" s="3" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
